--- a/Result/profitability/2949.xlsx
+++ b/Result/profitability/2949.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM20"/>
+  <dimension ref="A1:AM21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2970,6 +2970,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1544</v>
+      </c>
+      <c r="E21" t="n">
+        <v>211</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>41</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>28</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9037499999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11.36875</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.1900000000000001</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.2567567567567568</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.3599999999999994</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.02910266774454318</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.08823529411764708</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.008257638315441795</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
